--- a/docs/FASE0_campos_apolice_DO.xlsx
+++ b/docs/FASE0_campos_apolice_DO.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
@@ -57,7 +61,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,11 +106,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -111,22 +117,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -511,7 +523,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Paulo, a plataforma vai ler apólices D&amp;O em PDF e apontar as diferenças entre elas automaticamente. Para isso funcionar, alguém precisa dizer QUAIS diferenças importam. Esse alguém é você.</t>
+          <t>Paulo, imagine que um cliente te manda duas propostas de D&amp;O de seguradoras diferentes e pergunta: 'qual a diferença entre elas?'. Você não lê as 120 páginas. Você vai direto em uns 10 pontos que sabe de cor.</t>
         </is>
       </c>
     </row>
@@ -519,9 +531,9 @@
       <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>No Desafio 5 foram os seus limiares de chuva e vento que fizeram o sistema avisar as pessoas certas. Aqui é a mesma coisa: sem a sua lista, o programa compara tudo e não destaca nada.</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ESSA LISTA É O QUE EU PRECISO. Só isso.</t>
         </is>
       </c>
     </row>
@@ -531,76 +543,138 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>São duas abas para preencher:</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="8" customHeight="1">
-      <c r="A8" s="2" t="inlineStr"/>
+          <t>A diferença em relação ao Desafio 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Lá, você deu REGRAS: 'acima de 40 mm de chuva, avise o segurado'. O sistema decidia sozinho e disparava o alerta.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ABA 1 — Campos a comparar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Listei 12 candidatos com o que entendi que cada um significa. Para cada linha, diga na coluna amarela se vale comparar (SIM / NAO / TALVEZ) e escreva por quê em uma frase. Se eu escrevi alguma definição errada, corrija sem dó.</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Aqui é mais simples: você NÃO decide nada e NÃO compara nada. Você só diz ONDE OLHAR. O programa lê as duas apólices, acha esses pontos em cada uma e mostra lado a lado. Quem olha e decide é o corretor que usar a ferramenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="8" customHeight="1">
+      <c r="A10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Se faltou campo que você olha na prática, use as linhas vazias do fim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1">
-      <c r="A12" s="2" t="inlineStr"/>
+          <t>Por exemplo: se você marcar SIM no Limite Máximo de Indenização, o sistema vai cuspir algo assim:</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Apólice A: R$ 10 milhões   |   Apólice B: R$ 5 milhões   -&gt; DIFERENTE</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ABA 2 — Onde achar apólices</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Precisamos de pelo menos três apólices D&amp;O de seguradoras diferentes, documentos públicos. Se souber onde baixar, coloque o link. Se tiver o arquivo, me mande direto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Quanto preencher: se der, marque todos os 12. Se o tempo for curto, priorize marcar SIM nos 8 mais importantes — é o suficiente para começarmos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Ele não diz qual é melhor. Só mostra. Se você não colocar o LMI na lista, ele nem procura esse número — e o cliente perde a informação mais importante da comparação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>São duas abas para preencher:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="8" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ABA 1 — Onde olhar</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Prazo: até 17/09. É a primeira coisa do projeto e trava o trabalho de todo mundo, então quanto antes melhor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Listei 12 pontos com o que entendi que cada um significa. Para cada linha, diga na coluna amarela se vale olhar (SIM / NAO / TALVEZ). Na última coluna, escreva por que essa diferença pesa para o cliente — uma frase basta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>A primeira linha da aba já está preenchida como EXEMPLO, em verde. É exatamente esse nível de resposta que eu preciso.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Se eu escrevi alguma definição errada, corrija sem dó — eu chutei por leitura, você faz isso na prática.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Se faltou ponto que você olha e não está na lista, use as linhas vazias do fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="8" customHeight="1">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ABA 2 — Onde achar apólices</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Precisamos de pelo menos três apólices D&amp;O de seguradoras diferentes, documentos públicos. Se souber onde baixar, coloque o link. Se tiver o arquivo, me mande direto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Quanto preencher: se der, marque todos os 12. Se o tempo for curto, priorize marcar SIM nos 8 mais importantes — é o suficiente para começarmos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="8" customHeight="1">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Prazo: até 17/09. É a primeira coisa do projeto e trava o trabalho de todo mundo, então quanto antes melhor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Não precisa mexer em nada de programação. Preencha, salve e me devolva por WhatsApp.</t>
         </is>
@@ -617,14 +691,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -645,287 +719,314 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Comparar?</t>
+          <t>Olhar este campo?</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Por que importa (sua justificativa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+          <t>Se as duas apólices forem diferentes aqui, por que isso importa para o cliente?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
+          <t>EXEMPLO — Limite Máximo de Indenização</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Valor máximo que a seguradora paga no total da apólice</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Limite de Garantia, LMG, Capital Segurado</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Um limite menor pode deixar o cliente descoberto num sinistro grande. É o primeiro número que eu olho numa proposta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
           <t>Limite Máximo de Indenização (LMI)</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Valor máximo que a seguradora paga no total da apólice</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Limite de Garantia, Capital Segurado, LMG</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="8" t="n"/>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Franquia / Retenção</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Valor que o segurado paga antes de a cobertura começar</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Participação Obrigatória do Segurado, Retention, Dedutível</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="n"/>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Vigência</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Data de início e fim da cobertura</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Período de Vigência, Prazo de Seguro</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Retroatividade</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>A partir de que data atos anteriores à apólice ficam cobertos</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Data Retroativa, Cobertura Retroativa</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Prazo Complementar / Suplementar</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Tempo após o fim da apólice em que ainda se pode reclamar</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Extended Reporting Period, Prazo de Notificação</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Âmbito Geográfico</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Em que países a cobertura vale</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Abrangência Territorial, Jurisdição</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Definição de Segurado</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Quem exatamente está coberto (diretores, conselheiros, cônjuge, espólio)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Pessoa Segurada, Insured Person</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Custos de Defesa</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Se honorários advocatícios entram e se consomem o limite</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Despesas de Defesa, Defence Costs</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Cobertura para Multas Administrativas</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Se multas de órgãos reguladores são cobertas</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Penalidades Civis e Administrativas</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Exclusão de Atos Dolosos</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Como a apólice trata fraude e dolo comprovado</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Conduta Dolosa, Atos Fraudulentos</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Exclusão de Poluição / Ambiental</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Se danos ambientais ficam de fora</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Riscos Ambientais</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Cláusula de Rescisão</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Em que condições a apólice pode ser cancelada</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Cancelamento, Resilição</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n"/>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
+      <c r="E14" s="9" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>As linhas em amarelo são para você preencher. As seis últimas estão vazias de propósito: se faltou algum campo que você olha e que não está na lista, acrescente ali.</t>
         </is>
@@ -933,7 +1034,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SIM,NAO,TALVEZ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -979,83 +1080,83 @@
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>SUSEP</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Superintendência de Seguros Privados — condições gerais registradas</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>https://www.susep.gov.br</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n"/>
+      <c r="D2" s="9" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Site de seguradora</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Modelos de condições gerais publicados para consulta</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="8" t="n"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="9" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Corretora / material de mercado</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Condições padrão que circulam no setor</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="8" t="n"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="9" t="n"/>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Precisamos de pelo menos TRÊS apólices de seguradoras DIFERENTES. Comparar duas versões do mesmo modelo não demonstra nada. Podem ser condições gerais públicas — não precisa ser apólice de cliente, e não deve conter dado de ninguém.</t>
         </is>
